--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="106">
   <si>
     <t>参数项</t>
   </si>
@@ -804,6 +804,38 @@
 5、为空，如ubuntu-n13_Port=
 6、参数不存在
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool:true|false
+CM与OM通信用的，只有配置为true才会与OM通信，配置为false不与OM通信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM跟OM在同一台主机，sdbcm.conf配置参数：AutoStart=TRUE
+DiagLevel=3
+IsGeneral=TRUE
+OMAddress=ubuntu-n13:11785
+RestartCount=5
+RestartInterval=0
+defaultPort=11790
+ubuntu-n13_Port=11790
+CM跟OM不在同一台主机，sdbcm.conf配置参数：AutoStart=TRUE
+RestartCount=5
+RestartInterval=0
+defaultPort=11790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM与OM在同一个主机，添加有效配置
+2、CM与OM不在同一个主机，添加有效配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM与OM不在同一个主机，添加与OM在同一个主机才有的配置：DiagLevel=3
+IsGeneral=TRUE
+OMAddress=ubuntu-n13:11785
+ubuntu-n13_Port=11790</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -868,7 +900,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,6 +922,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -973,7 +1011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1011,38 +1049,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1338,7 +1385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
@@ -1374,29 +1421,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="15" customFormat="1" ht="114.75">
+    <row r="2" spans="1:7" s="13" customFormat="1" ht="114.75">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="127.5">
-      <c r="B3" s="13"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1412,7 +1459,7 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="140.25">
-      <c r="B4" s="13"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1428,7 +1475,7 @@
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="89.25">
-      <c r="B5" s="14"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1601,71 +1648,71 @@
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" s="15" customFormat="1" ht="38.25">
+    <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="16"/>
-    </row>
-    <row r="16" spans="1:7" s="15" customFormat="1" ht="25.5">
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="22"/>
+      <c r="C16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" s="15" customFormat="1" ht="51">
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:7" s="13" customFormat="1" ht="51">
       <c r="A17" s="6"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16" t="s">
+      <c r="B17" s="23"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="16"/>
+      <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:7" ht="40.5" customHeight="1">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="9" t="s">
         <v>89</v>
       </c>
       <c r="G18" s="5" t="s">
@@ -1673,133 +1720,147 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B19" s="9"/>
-      <c r="C19" s="21" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="9" t="s">
         <v>90</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="38.25">
-      <c r="B20" s="9"/>
-      <c r="C20" s="21" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="9" t="s">
         <v>88</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="9"/>
-      <c r="C21" s="21" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="9" t="s">
         <v>91</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="63.75">
-      <c r="B22" s="9"/>
-      <c r="C22" s="1" t="s">
+      <c r="B22" s="24"/>
+      <c r="C22" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="9" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="89.25">
-      <c r="B23" s="9"/>
-      <c r="C23" s="1" t="s">
+      <c r="B23" s="24"/>
+      <c r="C23" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="9"/>
-      <c r="C24" s="1" t="s">
+      <c r="B24" s="24"/>
+      <c r="C24" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="140.25">
-      <c r="B25" s="9"/>
-      <c r="C25" s="1" t="s">
+      <c r="B25" s="24"/>
+      <c r="C25" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="D28" s="20"/>
+    <row r="26" spans="1:7" ht="191.25">
+      <c r="B26" s="24"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="D29" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B25"/>
     <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B18:B26"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -15,8 +15,140 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+添加</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>localhost</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+添加</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>sparaRG</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+确认跟节点是否用的同一段代码校验</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数名不好理解，可服务不好</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
   <si>
     <t>参数项</t>
   </si>
@@ -43,10 +175,6 @@
   </si>
   <si>
     <t>组管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -98,44 +226,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>string，必填
-主机通信正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、正常通信的主机名，如：ubuntu-n12
 2、正常通信的IP地址，如：192.168.30.136</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、无法连接的主机名，如:test（test主机跟处理主机网络不通）
-2、无法连接的IP，如1.1.1.1（1.1.1.1与处理主机网络不通）
-3、无效的IP地址，如192.168.*
-4、空串，如：db.createCataRG(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>""</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, 11800, "/opt/sequoiadb/database/cata/11800")</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -194,14 +286,324 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>string，必填
-需确保数据管理员（安装时创建，默认为 sdbadmin）用户有写权限。
-路径不存在会自动创建</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、路径存在，且有写权限
 2、路径不存在，上级目录有写权限，如指定目录为/opt/sequoiadb，用户对/opt有写权限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Json对象，非必填
+参见数据库配置一节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、配置无效的config参数   ---参考创建节点config配置（吴艳）
+2、空串，如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟实际支持的字段参数个数一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>多参数情况，如创建组最多只能输入4个字段参数，实际输入5个字段（如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[...],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要求编目分区组上已经没有数据节点及协调节点的信息。
+删除编目分区组将会把该组中所有的编目节点都删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCataRG/getCoordRG/getRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listReplicaGroups</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM中不存在组
+2、存在组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件查询，如db.listReplicaGroups("test")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCoordRG
+语法：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不带条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件创建，如db.createCoordRG("test")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCoordRG()
+语法：db.removeCoordRG()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件删除，如removeCataRG
+语法：db.removeCoordRG("group1")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG
+语法：db.createRG(&lt;name&gt;)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、名称重复
+2、无效字符：包含（.）、包含美元符号（$）
+4、无效长度：空串、128B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG()
+语法：db.removeRG(&lt;name&gt;)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、组不存在
+2、空串，如db.removeRG("")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG
+语法：db.startRG(&lt;name&gt;)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CM管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -h
+ --help</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> --version
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动/停止/重启组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RestartCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RestartInterval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultPort</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料没列出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdbcm 的默认监听端口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;hostname&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_Port</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsGeneral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、true
+2、false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效取值：0、5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、无效值，如：test*、-1、yes/no
+2、为空
+3、参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、无效取值：-1、6、test@123
+2、为空，如：DiagLevel=
+3、参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、参数不存在
+2、参数值为：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1、50（待确认）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、参数不存在
+2、参数值为：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0、50（待确认）、超出范围？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、无效参数值：-1、test123*
+2、为空，如：RestartInterval=
+3、RestartCount参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、有效的hostname和端口，如：ubuntu-n13_Port=11790，跟实际安装的cm主机名和端口一致
+2、有效的主机名，端口不存在
+3、有效的主机名，端口不存在，且defaultPort 也不存在
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM与OM在同一个主机，添加有效配置
+2、CM与OM不在同一个主机，添加有效配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -213,67 +615,50 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Json对象，非必填
-参见数据库配置一节</t>
+    <t>string，必填
+主机通信正常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、无法连接的主机名，如:test（test主机跟处理主机网络不通）
+2、无法连接的IP，如1.1.1.1（1.1.1.1与处理主机网络不通）
+3、无效的IP地址，如192.168.*
+4、空串，如：db.createCataRG(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>""</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 11800, "/opt/sequoiadb/database/cata/11800")</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string，必填
+需确保数据管理员（安装时创建，默认为 sdbadmin）用户有写权限。
+路径不存在会自动创建</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、不配置config
 2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、配置无效的config参数   ---参考创建节点config配置（吴艳）
-2、空串，如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跟实际支持的字段参数个数一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>多参数情况，如创建组最多只能输入4个字段参数，实际输入5个字段（如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[...],</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>test</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要求编目分区组上已经没有数据节点及协调节点的信息。
-删除编目分区组将会把该组中所有的编目节点都删除。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -285,51 +670,12 @@
     <t>1、编目组包含数据节点信息
 2、编目组包含协调节点信息
 3、带条件删除，如removeCataRG
-语法：db.removeCoordRG("group1")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getCataRG/getCoordRG/getRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>组存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、组不存在
+语法：db.removeCataRG("group1")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、空组
 2、带条件查询，如db.getCatalogRG("test")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listReplicaGroups</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CM中不存在组
-2、存在组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件查询，如db.listReplicaGroups("test")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCoordRG
-语法：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不带条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件创建，如db.createCoordRG("test")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCoordRG()
-语法：db.removeCoordRG()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -339,20 +685,6 @@
   <si>
     <t>1、删除空组
 2、删除不为空的组（组内有节点）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件删除，如removeCataRG
-语法：db.removeCoordRG("group1")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createRG
-语法：db.createRG(&lt;name&gt;)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -362,14 +694,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、名称重复
-2、无效字符：包含（.）、包含美元符号（$）
-4、无效长度：空串、128B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeRG()
-语法：db.removeRG(&lt;name&gt;)</t>
+    <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -379,18 +704,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、组不存在
-2、空串，如db.removeRG("")</t>
+    <t>组存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string，必填
 指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startRG
-语法：db.startRG(&lt;name&gt;)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -404,12 +723,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CM管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
+    <t>bin/sdbcm/sdbcmart/sdbcmtop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -417,25 +731,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> -h
- --help</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>参数： --version</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> --version
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动/停止/重启组</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -456,27 +752,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bin/sdbcm/sdbcmart/sdbcmtop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RestartCount</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RestartInterval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defaultPort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bool:true|false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资料没列出</t>
+    <r>
+      <t>1、无效值，如：test*、-1、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yes/no、y/n、T/F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、为空，如：AutoStart=
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3、参数不存在</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiagLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -484,44 +805,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sdbcm 的默认监听端口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;hostname&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_Port</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AutoStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DiagLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsGeneral</t>
+    <t>bool:true|false
+CM与OM通信用的，只有配置为true才会与OM通信，配置为false不与OM通信</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -529,56 +814,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OM地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、true
-2、false</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有效取值：0、5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正确的OM主机和端口，如根据安装的OM配置为ubuntu-n13:11785</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">重启次数，即定义 sdbcm 对节点的最大重启次数。该参数不存在时默认置为-1，即不断重启。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>允许设置的最大值为？？？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、无效值，如：test*、-1、yes/no
-2、为空
-3、参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、无效值，如：test*、-1、yes/no
-2、为空，如：AutoStart=
-3、参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、无效取值：-1、6、test@123
-2、为空，如：DiagLevel=
-3、参数不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -590,8 +826,7 @@
   </si>
   <si>
     <r>
-      <t>1、参数不存在
-2、参数值为：</t>
+      <t>重启次数，即定义 sdbcm 对节点的最大重启次数。该参数不存在时默认置为</t>
     </r>
     <r>
       <rPr>
@@ -602,7 +837,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>-1、50（待确认）</t>
+      <t>-1</t>
     </r>
     <r>
       <rPr>
@@ -613,15 +848,9 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
+      <t xml:space="preserve">，即不断重启。
 </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、无效参数值：-2、</t>
-    </r>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -631,7 +860,24 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>超出范围？</t>
+      <t>允许设置的最大值为？？？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、无效参数值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2、超出范围？</t>
     </r>
     <r>
       <rPr>
@@ -691,48 +937,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1、参数不存在
-2、参数值为：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0、50（待确认）、超出范围？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t xml:space="preserve">正确的CM的监听端口
 </t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、无效参数值：-1、test123*
-2、为空，如：RestartInterval=
-3、RestartCount参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">正确的CM下节点的端口
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、非CM节点端口
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、非CM监听端口
 2、无效的端口，如test&amp;*1
 3、为空，如defaultPort=
 4、参数不存在
@@ -790,25 +1000,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">1、有效的hostname和端口，如：ubuntu-n13_Port=11790，跟实际安装的cm主机名和端口一致
-2、有效的主机名，端口不存在
-3、有效的主机名，端口不存在，且defaultPort 也不存在
+    <t xml:space="preserve">1、无效的主机名，如test*_Port=11790
+2、配置的端口非CM的监听端口，如实际CM监听端口为11790，配置为ubuntu-n13_Port=11791
+3、有效的主机名，端口不存在，且defaultPort 也不存在，且11790不是CM的监听端口
+4、为空，如ubuntu-n13_Port=
+5、参数不存在
+6、各节点该参数配置不一致
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、配置的hostname非本地CM的hostname
-2、无效的主机名，如test*_Port=11790
-3、配置的端口非本地CM的监听端口，如实际CM监听端口为11790，配置为ubuntu-n13_Port=11791
-4、有效的主机名，端口不存在，且defaultPort 也不存在，且11790不是CM的监听端口
-5、为空，如ubuntu-n13_Port=
-6、参数不存在
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool:true|false
-CM与OM通信用的，只有配置为true才会与OM通信，配置为false不与OM通信</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -827,15 +1025,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、CM与OM在同一个主机，添加有效配置
-2、CM与OM不在同一个主机，添加有效配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CM与OM不在同一个主机，添加与OM在同一个主机才有的配置：DiagLevel=3
+    <r>
+      <t xml:space="preserve">CM与OM不在同一个主机，添加与OM在同一个主机才有的配置：DiagLevel=3
 IsGeneral=TRUE
 OMAddress=ubuntu-n13:11785
-ubuntu-n13_Port=11790</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ubuntu-n13_Port=11790</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -843,7 +1049,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,6 +1104,27 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1011,7 +1238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1076,6 +1303,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1083,12 +1322,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1388,10 +1621,10 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="18" style="6" customWidth="1"/>
+    <col min="1" max="1" width="3.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="14.625" style="6" customWidth="1"/>
     <col min="3" max="3" width="11" style="6" customWidth="1"/>
-    <col min="4" max="4" width="32.375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20" style="6" customWidth="1"/>
     <col min="5" max="5" width="29.25" style="6" customWidth="1"/>
     <col min="6" max="6" width="31.875" style="6" customWidth="1"/>
     <col min="7" max="7" width="22.625" style="6" customWidth="1"/>
@@ -1400,10 +1633,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>0</v>
@@ -1418,75 +1651,75 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="13" customFormat="1" ht="114.75">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>14</v>
+      <c r="B2" s="25" t="s">
+        <v>13</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="127.5">
-      <c r="B3" s="22"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="140.25">
-      <c r="B4" s="22"/>
+    <row r="4" spans="1:7" ht="127.5">
+      <c r="B4" s="26"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" ht="89.25">
+      <c r="B5" s="27"/>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" ht="89.25">
-      <c r="B5" s="23"/>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -1497,351 +1730,351 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" ht="51">
+    <row r="7" spans="1:7" ht="76.5">
       <c r="B7" s="10" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="38.25">
       <c r="B8" s="10" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="25.5">
       <c r="B9" s="10" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="25.5">
       <c r="B10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="51">
+      <c r="B11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="76.5">
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" ht="51">
+      <c r="B13" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="76.5">
+      <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:7" ht="38.25">
-      <c r="B11" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="51">
-      <c r="B12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:7" ht="38.25">
-      <c r="B13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="51">
-      <c r="B14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>58</v>
+      <c r="C14" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25">
       <c r="A15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>70</v>
+        <v>43</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>84</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="26"/>
       <c r="C16" s="14" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" s="13" customFormat="1" ht="51">
       <c r="A17" s="6"/>
-      <c r="B17" s="23"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="53.25" customHeight="1">
+      <c r="B18" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1">
+      <c r="B19" s="28"/>
+      <c r="C19" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="51">
+      <c r="B20" s="28"/>
+      <c r="C20" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="102">
+      <c r="B21" s="28"/>
+      <c r="C21" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="76.5">
+      <c r="B22" s="28"/>
+      <c r="C22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="153">
+      <c r="B23" s="28"/>
+      <c r="C23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="63.75">
+      <c r="B24" s="28"/>
+      <c r="C24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="140.25">
+      <c r="B25" s="28"/>
+      <c r="C25" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="229.5">
+      <c r="B26" s="28"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="40.5" customHeight="1">
-      <c r="B18" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B19" s="24"/>
-      <c r="C19" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="38.25">
-      <c r="B20" s="24"/>
-      <c r="C20" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="24"/>
-      <c r="C21" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" ht="63.75">
-      <c r="B22" s="24"/>
-      <c r="C22" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" ht="89.25">
-      <c r="B23" s="24"/>
-      <c r="C23" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="24"/>
-      <c r="C24" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="140.25">
-      <c r="B25" s="24"/>
-      <c r="C25" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="191.25">
-      <c r="B26" s="24"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>105</v>
+      <c r="F26" s="22" t="s">
+        <v>106</v>
       </c>
       <c r="G26" s="5"/>
     </row>
@@ -1865,6 +2098,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
   <si>
     <t>参数项</t>
   </si>
@@ -226,66 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、正常通信的主机名，如：ubuntu-n12
-2、正常通信的IP地址，如：192.168.30.136</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">int，必填
-端口不被占用，包括往后顺延的3个端口
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>端口取值范围（0~65535）？？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、端口未被占用，如配置未被占用的11800端口
-2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、端口被占用，或往后顺延的3个端口中其中1个端口被占用
-2、端口无效，如test123*、-1、65536
-3、空串，如db.createCataRG("sdbserver1"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, , </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"/opt/sequoiadb/database/cata/11800")
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、路径存在，且有写权限
 2、路径不存在，上级目录有写权限，如指定目录为/opt/sequoiadb，用户对/opt有写权限</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -368,11 +308,6 @@
   </si>
   <si>
     <t>带条件查询，如db.listReplicaGroups("test")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCoordRG
-语法：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -437,16 +372,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> -h
- --help</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> --version
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>启动/停止/重启组</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -505,11 +430,6 @@
   </si>
   <si>
     <t>OM地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、true
-2、false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -529,89 +449,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1、参数不存在
-2、参数值为：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1、50（待确认）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、参数不存在
-2、参数值为：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0、50（待确认）、超出范围？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、无效参数值：-1、test123*
 2、为空，如：RestartInterval=
 3、RestartCount参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、有效的hostname和端口，如：ubuntu-n13_Port=11790，跟实际安装的cm主机名和端口一致
-2、有效的主机名，端口不存在
-3、有效的主机名，端口不存在，且defaultPort 也不存在
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CM与OM在同一个主机，添加有效配置
-2、CM与OM不在同一个主机，添加有效配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、指定目录没有写权限
-2、目录名无效，如/opt/test123@#
-3、空串，如db.createCataRG("sdbserver1", 11800, "")
-4、路径无效，如不带路径标记”/”（opt）
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -657,16 +497,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、不配置config
-2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、空组
-2、编目组包含编目节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、编目组包含数据节点信息
 2、编目组包含协调节点信息
 3、带条件删除，如removeCataRG
@@ -688,12 +518,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、名称唯一
-2、有效字符：数字、中文、字母开头带有效特殊字符（如group_1）
-3、有效长度：1B、127B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -705,11 +529,6 @@
   </si>
   <si>
     <t>组存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string，必填
-指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -797,10 +616,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DiagLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[0~5]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -822,77 +637,6 @@
 2、端口错误，如ubuntu-n13主机OM端口为8888，配置为ubuntu-n13:7777
 3、空串，如OMAddress=  或  OMAddress=ubuntu-n13:  或  OMAddress=:11785
 4、参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>重启次数，即定义 sdbcm 对节点的最大重启次数。该参数不存在时默认置为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">，即不断重启。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>允许设置的最大值为？？？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、无效参数值：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-2、超出范围？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">、test123*
-2、为空，如：RestartCount=
-3、RestartInterval参数不存在
-</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -997,16 +741,6 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、无效的主机名，如test*_Port=11790
-2、配置的端口非CM的监听端口，如实际CM监听端口为11790，配置为ubuntu-n13_Port=11791
-3、有效的主机名，端口不存在，且defaultPort 也不存在，且11790不是CM的监听端口
-4、为空，如ubuntu-n13_Port=
-5、参数不存在
-6、各节点该参数配置不一致
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1042,6 +776,274 @@
       </rPr>
       <t>ubuntu-n13_Port=11790</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">int，必填
+端口不被占用，包括往后顺延的3个端口
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>端口取值范围（0~65535）？？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、正常通信的主机名，如：ubuntu-n12
+2、正常通信的IP地址，如：192.168.30.136
+3、指定主机名为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>localhost</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、端口未被占用，如配置未被占用的11800端口
+2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用
+3、有效取值：0、65535</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、端口被占用，或往后顺延的3个端口中其中1个端口被占用
+2、端口无效，如test123*、-1、65536
+3、空串，如db.createCataRG("sdbserver1"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"/opt/sequoiadb/database/cata/11800")</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、指定目录没有写权限
+2、目录名无效，如/opt/test123@#
+3、空串，如db.createCataRG("sdbserver1", 11800, "")
+4、路径无效，如不带路径标记”/”（opt）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不配置config
+2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、空组
+2、编目组包含编目节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCoordRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、名称唯一
+2、有效字符：数字、中文、字母开头带有效特殊字符（如group_1）
+3、有效长度：1B、127B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string，必填
+指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -h
+ --help</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> --version
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、true
+2、false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、参数不存在
+2、参数值为：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1、50（待确认）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、无效参数值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2、超出范围？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、test123*
+2、为空，如：RestartCount=
+3、RestartInterval参数不存在</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、参数不存在
+2、参数值为：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0、50（待确认）、超出范围？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>重启次数，即定义 sdbcm 对节点的最大重启次数。该参数不存在时默认置为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，即不断重启。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>允许设置的最大值为？？？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiagLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、有效的hostname和端口，如：ubuntu-n13_Port=11790，跟实际安装的cm主机名和端口一致
+2、有效的主机名，端口不存在
+3、有效的主机名，端口不存在，且defaultPort 也不存在
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、无效的主机名，如test*_Port=11790
+2、配置的端口非CM的监听端口，如实际CM监听端口为11790，配置为ubuntu-n13_Port=11791
+3、有效的主机名，端口不存在，且defaultPort 也不存在，且11790不是CM的监听端口
+4、为空，如ubuntu-n13_Port=
+5、参数不存在
+6、各节点该参数配置不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM与OM在同一个主机，添加有效配置
+2、CM与OM不在同一个主机，添加有效配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1238,7 +1240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1310,6 +1312,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1621,13 +1629,13 @@
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="6.625" style="6" customWidth="1"/>
     <col min="2" max="2" width="14.625" style="6" customWidth="1"/>
     <col min="3" max="3" width="11" style="6" customWidth="1"/>
-    <col min="4" max="4" width="20" style="6" customWidth="1"/>
-    <col min="5" max="5" width="29.25" style="6" customWidth="1"/>
-    <col min="6" max="6" width="31.875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="22.625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="27.25" style="6" customWidth="1"/>
+    <col min="5" max="5" width="29.625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="33.875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="6" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
@@ -1654,427 +1662,427 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="13" customFormat="1" ht="114.75">
+    <row r="2" spans="1:7" s="13" customFormat="1" ht="102">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G2" s="14"/>
     </row>
-    <row r="3" spans="1:7" ht="127.5">
-      <c r="B3" s="26"/>
+    <row r="3" spans="1:7" ht="76.5">
+      <c r="B3" s="28"/>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
+      <c r="D3" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>89</v>
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="127.5">
-      <c r="B4" s="26"/>
+    <row r="4" spans="1:7" ht="89.25">
+      <c r="B4" s="28"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>67</v>
+        <v>57</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>90</v>
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" ht="89.25">
-      <c r="B5" s="27"/>
+    <row r="5" spans="1:7" ht="76.5">
+      <c r="B5" s="29"/>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>71</v>
+        <v>16</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>91</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" ht="76.5">
+    <row r="6" spans="1:7" ht="63.75">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" ht="51">
+      <c r="B7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" ht="76.5">
-      <c r="B7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>72</v>
+      <c r="E7" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="38.25">
       <c r="B8" s="10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>93</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="25.5">
       <c r="B9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="21" t="s">
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="51">
+      <c r="B11" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="C11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>31</v>
-      </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" ht="25.5">
-      <c r="B10" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:7" ht="51">
-      <c r="B11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>36</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="76.5">
       <c r="B12" s="10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>77</v>
+      <c r="E12" s="25" t="s">
+        <v>95</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="51">
       <c r="B13" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:7" ht="76.5">
+    <row r="14" spans="1:7" ht="51">
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>81</v>
+        <v>62</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>96</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25">
       <c r="A15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>84</v>
+        <v>38</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>67</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="26"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="14" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" s="13" customFormat="1" ht="51">
       <c r="A17" s="6"/>
-      <c r="B17" s="27"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="53.25" customHeight="1">
+      <c r="B18" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="53.25" customHeight="1">
-      <c r="B18" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>55</v>
-      </c>
       <c r="D18" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>58</v>
+        <v>73</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G18" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1">
+      <c r="B19" s="30"/>
+      <c r="C19" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="51">
+      <c r="B20" s="30"/>
+      <c r="C20" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B19" s="28"/>
-      <c r="C19" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="51">
-      <c r="B20" s="28"/>
-      <c r="C20" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="28"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="23" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" ht="76.5">
-      <c r="B22" s="28"/>
+    <row r="22" spans="1:7" ht="51">
+      <c r="B22" s="30"/>
       <c r="C22" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>99</v>
+        <v>42</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="153">
-      <c r="B23" s="28"/>
+    <row r="23" spans="1:7" ht="102">
+      <c r="B23" s="30"/>
       <c r="C23" s="9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>63</v>
+        <v>80</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>102</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="28"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="140.25">
-      <c r="B25" s="28"/>
+    <row r="25" spans="1:7" ht="127.5">
+      <c r="B25" s="30"/>
       <c r="C25" s="24" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>104</v>
+        <v>83</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>106</v>
       </c>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="229.5">
-      <c r="B26" s="28"/>
+    <row r="26" spans="1:7" ht="204">
+      <c r="B26" s="30"/>
       <c r="C26" s="9"/>
       <c r="D26" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>106</v>
+        <v>84</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>85</v>
       </c>
       <c r="G26" s="5"/>
     </row>

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -53,6 +53,32 @@
             <family val="2"/>
           </rPr>
           <t>localhost</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+跟创建节点的参数配置交叉测试</t>
         </r>
       </text>
     </comment>
@@ -148,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="107">
   <si>
     <t>参数项</t>
   </si>
@@ -175,12 +201,6 @@
   </si>
   <si>
     <t>组管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string,必填
-同一个数据库对象中，分区组名唯一。
-不能是空串，含点（.）或者美元符号（$），并且长度不能超过127B。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -226,11 +246,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、路径存在，且有写权限
-2、路径不存在，上级目录有写权限，如指定目录为/opt/sequoiadb，用户对/opt有写权限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Config</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -299,11 +314,6 @@
   </si>
   <si>
     <t>listReplicaGroups</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CM中不存在组
-2、存在组</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -430,10 +440,6 @@
   </si>
   <si>
     <t>OM地址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有效取值：0、5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -528,10 +534,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>组存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>组存在，且未启动</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -571,10 +573,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bool:true|false</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1、无效值，如：test*、-1、</t>
     </r>
@@ -616,20 +614,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[0~5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool:true|false
-CM与OM通信用的，只有配置为true才会与OM通信，配置为false不与OM通信</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OMAddress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正确的OM主机和端口，如根据安装的OM配置为ubuntu-n13:11785</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -637,52 +622,6 @@
 2、端口错误，如ubuntu-n13主机OM端口为8888，配置为ubuntu-n13:7777
 3、空串，如OMAddress=  或  OMAddress=ubuntu-n13:  或  OMAddress=:11785
 4、参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>重启间隔，即定义 sdbcm 的最大重启间隔，单位是分钟。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>该参数与 RestartCount 结合定义了重启间隔内 sdbcm 对节点的最大重启次数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">，超出时则
-不再重启。该参数不存在时默认置为0，即不考虑重启间隔。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>允许设置的最大值为？？？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">正确的CM的监听端口
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -799,31 +738,6 @@
   </si>
   <si>
     <r>
-      <t>1、正常通信的主机名，如：ubuntu-n12
-2、正常通信的IP地址，如：192.168.30.136
-3、指定主机名为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>localhost</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、端口未被占用，如配置未被占用的11800端口
-2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用
-3、有效取值：0、65535</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>1、端口被占用，或往后顺延的3个端口中其中1个端口被占用
 2、端口无效，如test123*、-1、65536
 3、空串，如db.createCataRG("sdbserver1"</t>
@@ -860,27 +774,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、不配置config
-2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、空组
 2、编目组包含编目节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>组存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CreateCoordRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、名称唯一
-2、有效字符：数字、中文、字母开头带有效特殊字符（如group_1）
-3、有效长度：1B、127B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -896,11 +795,6 @@
   <si>
     <t xml:space="preserve"> --version
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、true
-2、false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -982,54 +876,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>重启次数，即定义 sdbcm 对节点的最大重启次数。该参数不存在时默认置为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">，即不断重启。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>允许设置的最大值为？？？</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DiagLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、有效的hostname和端口，如：ubuntu-n13_Port=11790，跟实际安装的cm主机名和端口一致
-2、有效的主机名，端口不存在
-3、有效的主机名，端口不存在，且defaultPort 也不存在
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1046,12 +893,387 @@
 2、CM与OM不在同一个主机，添加有效配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、正常通信的主机名，如：ubuntu-n12
+2、正常通信的IP地址，如：192.168.30.136</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3、指定主机名为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>localhost</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、端口未被占用，如配置未被占用的11800端口
+2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3、有效取值：0、65535</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、路径存在，且有写权限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、路径不存在，上级目录有写权限，如指定目录为/opt/sequoiadb，用户对/opt有写权限</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1、CM中不存在组
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2、存在组</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string,必填
+同一个数据库对象中，分区组名唯一。name不能是空串，含点（.）或者美元符号（$），并且长度不能超过127B。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、名称唯一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、有效字符：数字、中文、字母开头带有效特殊字符（如group_1）
+3、有效长度：1B、127B</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、true，默认配置为true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、false</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0~5]，默认配置为3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、检查默认配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、有效取值：0、5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool:true|false，默认为true
+CM与OM通信用的，只有配置为true才会与OM通信，配置为false不与OM通信。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool:true|false，默认为true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、false</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正确的OM主机和端口，如根据安装的OM配置为ubuntu-n13:11785</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>重启次数，即定义 sdbcm 对节点的最大重启次数。该参数不存在时默认置为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，即不断重启。默认为5
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>允许设置的最大值为？？？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>重启间隔，即定义 sdbcm 的最大重启间隔，单位是分钟。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>该参数与 RestartCount 结合定义了重启间隔内 sdbcm 对节点的最大重启次数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，超出时则不再重启。该参数不存在时默认置为0，即不考虑重启间隔。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>允许设置的最大值为？？？</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">正确的CM的监听端口
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、有效的hostname和端口，如：ubuntu-n13_Port=11790，跟实际安装的cm主机名和端口一致</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、有效的主机名，端口不存在
+3、有效的主机名，端口不存在，且defaultPort 也不存在
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、不配置config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1127,6 +1349,22 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1240,7 +1478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1323,6 +1561,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1330,6 +1574,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1338,6 +1588,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+    </mruColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1641,10 +1896,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>11</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>0</v>
@@ -1659,75 +1914,75 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="13" customFormat="1" ht="102">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="27" t="s">
-        <v>13</v>
+      <c r="B2" s="29" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="76.5">
-      <c r="B3" s="28"/>
+      <c r="B3" s="30"/>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>88</v>
+        <v>75</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>90</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="89.25">
-      <c r="B4" s="28"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" ht="76.5">
+      <c r="B5" s="31"/>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" ht="76.5">
-      <c r="B5" s="29"/>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -1737,352 +1992,352 @@
         <v>7</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="26" t="s">
-        <v>18</v>
+      <c r="E6" s="33" t="s">
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="51">
       <c r="B7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>92</v>
+      <c r="E7" s="27" t="s">
+        <v>78</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="38.25">
       <c r="B8" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>93</v>
+        <v>22</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="25.5">
       <c r="B9" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>92</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="25" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>25</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="51">
       <c r="B11" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="63.75">
+      <c r="B12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="21" t="s">
+      <c r="D12" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>31</v>
-      </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="76.5">
-      <c r="B12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>34</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="51">
       <c r="B13" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>22</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="51">
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>65</v>
+        <v>80</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>60</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25">
       <c r="A15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>67</v>
+        <v>35</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>62</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="28"/>
+      <c r="B16" s="30"/>
       <c r="C16" s="14" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" s="13" customFormat="1" ht="51">
       <c r="A17" s="6"/>
-      <c r="B17" s="29"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="53.25" customHeight="1">
+      <c r="B18" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1">
+      <c r="B19" s="32"/>
+      <c r="C19" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="51">
+      <c r="B20" s="32"/>
+      <c r="C20" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="102">
+      <c r="B21" s="32"/>
+      <c r="C21" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="63.75">
+      <c r="B22" s="32"/>
+      <c r="C22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="102">
+      <c r="B23" s="32"/>
+      <c r="C23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="63.75">
+      <c r="B24" s="32"/>
+      <c r="C24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="14" t="s">
+      <c r="D24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="53.25" customHeight="1">
-      <c r="B18" s="30" t="s">
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="127.5">
+      <c r="B25" s="32"/>
+      <c r="C25" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="18" t="s">
+      <c r="E25" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="204">
+      <c r="B26" s="32"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="22" t="s">
+      <c r="E26" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>74</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B19" s="30"/>
-      <c r="C19" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="51">
-      <c r="B20" s="30"/>
-      <c r="C20" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="30"/>
-      <c r="C21" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" ht="51">
-      <c r="B22" s="30"/>
-      <c r="C22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" ht="102">
-      <c r="B23" s="30"/>
-      <c r="C23" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="30"/>
-      <c r="C24" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="127.5">
-      <c r="B25" s="30"/>
-      <c r="C25" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="204">
-      <c r="B26" s="30"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>85</v>
       </c>
       <c r="G26" s="5"/>
     </row>

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -188,15 +188,6 @@
     <t>无效数据</t>
   </si>
   <si>
-    <t>Host</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Dbpath</t>
-  </si>
-  <si>
     <t>参数个数</t>
   </si>
   <si>
@@ -213,40 +204,6 @@
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CreateCataRG
-语法：db.createCataRG(&lt;host&gt;,&lt;service&gt;,&lt;dbpath&gt;,[config])
-格式：{"&lt;主机名/主机IP&gt;",&lt;端口号&gt;,"&lt;数据文件路径&gt;",[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>数据库配置参数对象</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Config</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -255,11 +212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、配置无效的config参数   ---参考创建节点config配置（吴艳）
-2、空串，如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>跟实际支持的字段参数个数一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,11 +249,6 @@
   </si>
   <si>
     <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要求编目分区组上已经没有数据节点及协调节点的信息。
-删除编目分区组将会把该组中所有的编目节点都删除。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -507,11 +454,6 @@
 2、编目组包含协调节点信息
 3、带条件删除，如removeCataRG
 语法：db.removeCataRG("group1")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、空组
-2、带条件查询，如db.getCatalogRG("test")</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -935,33 +877,6 @@
     <r>
       <rPr>
         <sz val="10.5"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1、端口未被占用，如配置未被占用的11800端口
-2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3、有效取值：0、65535</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <family val="3"/>
@@ -1266,6 +1181,94 @@
       <t xml:space="preserve">
 2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CreateCataRG
+语法：db.createCataRG(&lt;host&gt;,&lt;service&gt;,&lt;dbpath&gt;,[config])
+格式：{"&lt;主机名/主机IP&gt;",&lt;端口号&gt;,"&lt;数据文件路径&gt;",[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数据库配置参数对象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Service</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbpath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、端口未被占用，如配置未被占用的11800端口
+2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3、有效取值：0、65535
+4、服务名</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、配置无效的config参数   ---参考创建节点config配置（吴艳）
+2、空串，如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要求编目分区组上已经没有数据节点及协调节点的信息。
+删除编目分区组将会把该组中所有的编目节点都删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件查询，如db.getCatalogRG("test")</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1478,7 +1481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1567,6 +1570,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1574,12 +1589,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1896,10 +1905,10 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>0</v>
@@ -1914,430 +1923,430 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="13" customFormat="1" ht="102">
       <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G2" s="14"/>
     </row>
-    <row r="3" spans="1:7" ht="76.5">
-      <c r="B3" s="30"/>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>76</v>
+    <row r="3" spans="1:7" ht="89.25">
+      <c r="B3" s="34"/>
+      <c r="C3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>68</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="89.25">
-      <c r="B4" s="30"/>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>77</v>
+      <c r="B4" s="34"/>
+      <c r="C4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>69</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="76.5">
-      <c r="B5" s="31"/>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
+      <c r="B5" s="35"/>
+      <c r="C5" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="63.75">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" ht="51">
+      <c r="B7" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" ht="25.5">
+      <c r="B8" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="25.5">
+      <c r="B9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="C9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" ht="51">
-      <c r="B7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" ht="38.25">
-      <c r="B8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" ht="25.5">
-      <c r="B9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>24</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="25" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>26</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="51">
       <c r="B11" s="25" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="63.75">
       <c r="B12" s="10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="51">
       <c r="B13" s="10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>22</v>
+        <v>51</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>15</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="51">
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>60</v>
+        <v>72</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>52</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25">
       <c r="A15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>54</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="30"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="14" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" s="13" customFormat="1" ht="51">
       <c r="A17" s="6"/>
-      <c r="B17" s="31"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="53.25" customHeight="1">
+      <c r="B18" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="53.25" customHeight="1">
-      <c r="B18" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>45</v>
-      </c>
       <c r="D18" s="18" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E18" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="25.5" customHeight="1">
+      <c r="B19" s="36"/>
+      <c r="C19" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="51">
+      <c r="B20" s="36"/>
+      <c r="C20" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="102">
+      <c r="B21" s="36"/>
+      <c r="C21" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="63.75">
+      <c r="B22" s="36"/>
+      <c r="C22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="102">
+      <c r="B23" s="36"/>
+      <c r="C23" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="63.75">
+      <c r="B24" s="36"/>
+      <c r="C24" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B19" s="32"/>
-      <c r="C19" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="18" t="s">
+      <c r="F24" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="127.5">
+      <c r="B25" s="36"/>
+      <c r="C25" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="51">
-      <c r="B20" s="32"/>
-      <c r="C20" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="32"/>
-      <c r="C21" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" ht="63.75">
-      <c r="B22" s="32"/>
-      <c r="C22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" ht="102">
-      <c r="B23" s="32"/>
-      <c r="C23" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="32"/>
-      <c r="C24" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="127.5">
-      <c r="B25" s="32"/>
-      <c r="C25" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>105</v>
-      </c>
       <c r="F25" s="26" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" ht="204">
-      <c r="B26" s="32"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="9"/>
       <c r="D26" s="28" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G26" s="5"/>
     </row>

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -272,22 +272,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>带条件创建，如db.createCoordRG("test")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCoordRG()
-语法：db.removeCoordRG()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>带条件删除，如removeCataRG
 语法：db.removeCoordRG("group1")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createRG
-语法：db.createRG(&lt;name&gt;)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -301,11 +287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>removeRG()
-语法：db.removeRG(&lt;name&gt;)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、组不存在
 2、空串，如db.removeRG("")</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -320,11 +301,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -375,10 +351,6 @@
       </rPr>
       <t>_Port</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AutoStart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -495,13 +467,6 @@
   </si>
   <si>
     <t>参数： --version</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>service sdbcm start/stop/restart
-./sdbcm start/stop/restart
-./sdbcmart
-./sdbstop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -721,10 +686,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CreateCoordRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string，必填
 指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -822,15 +783,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、无效的主机名，如test*_Port=11790
-2、配置的端口非CM的监听端口，如实际CM监听端口为11790，配置为ubuntu-n13_Port=11791
-3、有效的主机名，端口不存在，且defaultPort 也不存在，且11790不是CM的监听端口
-4、为空，如ubuntu-n13_Port=
-5、参数不存在
-6、各节点该参数配置不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、CM与OM在同一个主机，添加有效配置
 2、CM与OM不在同一个主机，添加有效配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -976,41 +928,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[0~5]，默认配置为3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1、检查默认配置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、有效取值：0、5</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool:true|false，默认为true
-CM与OM通信用的，只有配置为true才会与OM通信，配置为false不与OM通信。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bool:true|false，默认为true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1127,6 +1044,160 @@
   <si>
     <t xml:space="preserve">正确的CM的监听端口
 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、不配置config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CreateCataRG
+语法：db.createCataRG(&lt;host&gt;,&lt;service&gt;,&lt;dbpath&gt;,[config])
+格式：{"&lt;主机名/主机IP&gt;",&lt;端口号&gt;,"&lt;数据文件路径&gt;",[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数据库配置参数对象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Service</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbpath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、端口未被占用，如配置未被占用的11800端口
+2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3、有效取值：0、65535
+4、服务名</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、配置无效的config参数   ---参考创建节点config配置（吴艳）
+2、空串，如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要求编目分区组上已经没有数据节点及协调节点的信息。
+删除编目分区组将会把该组中所有的编目节点都删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件查询，如db.getCatalogRG("test")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCoordRG()
+语法：db.removeCoordRG()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCoordRG
+语法：
+db.createCoordRG()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG
+语法：db.createRG(&lt;name&gt;)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG()
+语法：db.removeRG(&lt;name&gt;)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件创建，如db.createCoordRG("test")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、不带参数执行，如./sdbcm
+2、输入参数无效，如./sdbcm -v  或  ./sdbcm restart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>service sdbcm start|stop|status|restart
+./sdbcmart
+./sdbstop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AutoStart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1153,8 +1224,22 @@
       <t xml:space="preserve">
 2、有效的主机名，端口不存在
 3、有效的主机名，端口不存在，且defaultPort 也不存在
-</t>
-    </r>
+4、defaultPort配置正确，&lt;hostname&gt;_Port参数不存在
+5、defaultPort和&lt;hostname&gt;_Port参数均不存在，正确的端口为默认的11790</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、无效的主机名，如test*_Port=11790
+2、配置的端口非CM的监听端口，如实际CM监听端口为11790，配置为ubuntu-n13_Port=11791
+3、defaultPort和&lt;hostname&gt;_Port参数均不存在，且11790不是CM的监听端口
+4、为空，如ubuntu-n13_Port=
+6、各节点该参数配置不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool:true|false，默认为true
+CM与OM通信用的，配置为true时在sdbcm启动的时候会去OMAddress指定的sdbom中查询是否有没有完成的任务；配置为false的时候则不会去OM查询。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1167,7 +1252,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1、不配置config</t>
+      <t>1、检查默认配置</t>
     </r>
     <r>
       <rPr>
@@ -1179,96 +1264,13 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-2、参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>CreateCataRG
-语法：db.createCataRG(&lt;host&gt;,&lt;service&gt;,&lt;dbpath&gt;,[config])
-格式：{"&lt;主机名/主机IP&gt;",&lt;端口号&gt;,"&lt;数据文件路径&gt;",[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>数据库配置参数对象</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>]}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Service</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dbpath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1、端口未被占用，如配置未被占用的11800端口
-2、往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3、有效取值：0、65535
-4、服务名</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、配置无效的config参数   ---参考创建节点config配置（吴艳）
-2、空串，如：db.createCataRG("sdbserver1", 11800, "/opt/sequoiadb/database/cata/11800",[])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>要求编目分区组上已经没有数据节点及协调节点的信息。
-删除编目分区组将会把该组中所有的编目节点都删除。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件查询，如db.getCatalogRG("test")</t>
+2、有效取值：0、1、2、3、4、5</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0~5]，默认配置为3
+从0~5分别为：SEVERE, ERROR, EVENT, WARNING, INFO, DEBUG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1481,7 +1483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1582,6 +1584,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1589,6 +1597,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1930,68 +1944,68 @@
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="33" t="s">
-        <v>98</v>
+      <c r="B2" s="35" t="s">
+        <v>85</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="89.25">
-      <c r="B3" s="34"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="30" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="89.25">
-      <c r="B4" s="34"/>
+      <c r="B4" s="36"/>
       <c r="C4" s="30" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="76.5">
-      <c r="B5" s="35"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="30" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -2017,13 +2031,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -2041,7 +2055,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -2056,16 +2070,16 @@
         <v>13</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="25" t="s">
-        <v>71</v>
+    <row r="10" spans="1:7" ht="51">
+      <c r="B10" s="33" t="s">
+        <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>13</v>
@@ -2076,277 +2090,277 @@
       <c r="E10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>19</v>
+      <c r="F10" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="51">
-      <c r="B11" s="25" t="s">
-        <v>20</v>
+      <c r="B11" s="33" t="s">
+        <v>94</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>48</v>
+      <c r="D11" s="33" t="s">
+        <v>42</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" ht="63.75">
+      <c r="B12" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="63.75">
-      <c r="B12" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>24</v>
-      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="51">
-      <c r="B13" s="10" t="s">
-        <v>25</v>
+      <c r="B13" s="33" t="s">
+        <v>97</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>15</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="51">
-      <c r="B14" s="1" t="s">
-        <v>27</v>
+      <c r="B14" s="34" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>72</v>
+        <v>44</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>64</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25">
+    <row r="15" spans="1:7" s="13" customFormat="1" ht="38.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>54</v>
+        <v>24</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>48</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>29</v>
+        <v>65</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>99</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="34"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="14"/>
+        <v>66</v>
+      </c>
+      <c r="F16" s="40"/>
       <c r="G16" s="14"/>
     </row>
-    <row r="17" spans="1:7" s="13" customFormat="1" ht="51">
+    <row r="17" spans="1:7" s="13" customFormat="1" ht="76.5">
       <c r="A17" s="6"/>
-      <c r="B17" s="35"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="53.25" customHeight="1">
+      <c r="B18" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="54" customHeight="1">
+      <c r="B19" s="38"/>
+      <c r="C19" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="76.5">
+      <c r="B20" s="38"/>
+      <c r="C20" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" ht="102">
+      <c r="B21" s="38"/>
+      <c r="C21" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" ht="63.75">
+      <c r="B22" s="38"/>
+      <c r="C22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="102">
+      <c r="B23" s="38"/>
+      <c r="C23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" ht="63.75">
+      <c r="B24" s="38"/>
+      <c r="C24" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E24" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="140.25">
+      <c r="B25" s="38"/>
+      <c r="C25" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="E25" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="204">
+      <c r="B26" s="38"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="53.25" customHeight="1">
-      <c r="B18" s="36" t="s">
+      <c r="E26" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>59</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25.5" customHeight="1">
-      <c r="B19" s="36"/>
-      <c r="C19" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="51">
-      <c r="B20" s="36"/>
-      <c r="C20" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="36"/>
-      <c r="C21" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" ht="63.75">
-      <c r="B22" s="36"/>
-      <c r="C22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" ht="102">
-      <c r="B23" s="36"/>
-      <c r="C23" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="36"/>
-      <c r="C24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" ht="127.5">
-      <c r="B25" s="36"/>
-      <c r="C25" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="204">
-      <c r="B26" s="36"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>66</v>
       </c>
       <c r="G26" s="5"/>
     </row>
@@ -2362,10 +2376,11 @@
       <c r="D29" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B18:B26"/>
+    <mergeCell ref="F15:F16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
+++ b/internal_doc/05.测试设计/参数校验/集群管理参数校验测试设计_组管理 CM管理.xlsx
@@ -368,12 +368,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、无效取值：-1、6、test@123
-2、为空，如：DiagLevel=
-3、参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、无效参数值：-1、test123*
 2、为空，如：RestartInterval=
 3、RestartCount参数不存在</t>
@@ -720,36 +714,6 @@
   </si>
   <si>
     <r>
-      <t>1、无效参数值：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-2、超出范围？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>、test123*
-2、为空，如：RestartCount=
-3、RestartInterval参数不存在</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>1、参数不存在
 2、参数值为：</t>
     </r>
@@ -1271,6 +1235,42 @@
   <si>
     <t>[0~5]，默认配置为3
 从0~5分别为：SEVERE, ERROR, EVENT, WARNING, INFO, DEBUG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、无效取值：-1、6、test@123
+2、为空，如：DiagLevel=
+3、参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、无效参数值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2、超出范围？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、test123*
+2、为空，如：RestartCount=
+3、RestartCount参数不存在</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1483,7 +1483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1582,6 +1582,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1944,68 +1947,68 @@
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="89.25">
+      <c r="B3" s="37"/>
+      <c r="C3" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D3" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" ht="89.25">
+      <c r="B4" s="37"/>
+      <c r="C4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="D4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" ht="89.25">
-      <c r="B3" s="36"/>
-      <c r="C3" s="30" t="s">
+      <c r="E4" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" ht="76.5">
+      <c r="B5" s="38"/>
+      <c r="C5" s="30" t="s">
         <v>87</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" ht="89.25">
-      <c r="B4" s="36"/>
-      <c r="C4" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" ht="76.5">
-      <c r="B5" s="37"/>
-      <c r="C5" s="30" t="s">
-        <v>89</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -2031,13 +2034,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -2055,7 +2058,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -2070,7 +2073,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>17</v>
@@ -2079,7 +2082,7 @@
     </row>
     <row r="10" spans="1:7" ht="51">
       <c r="B10" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>13</v>
@@ -2091,22 +2094,22 @@
         <v>18</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="51">
       <c r="B11" s="33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>42</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>43</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>19</v>
@@ -2115,16 +2118,16 @@
     </row>
     <row r="12" spans="1:7" ht="63.75">
       <c r="B12" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>21</v>
@@ -2133,13 +2136,13 @@
     </row>
     <row r="13" spans="1:7" ht="51">
       <c r="B13" s="33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>15</v>
@@ -2154,16 +2157,16 @@
         <v>23</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>46</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>47</v>
       </c>
       <c r="G14" s="5"/>
     </row>
@@ -2171,155 +2174,155 @@
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>99</v>
+        <v>64</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>97</v>
       </c>
       <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" ht="25.5">
       <c r="A16" s="6"/>
-      <c r="B16" s="36"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="40"/>
+        <v>65</v>
+      </c>
+      <c r="F16" s="41"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" s="13" customFormat="1" ht="76.5">
       <c r="A17" s="6"/>
-      <c r="B17" s="37"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F17" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="53.25" customHeight="1">
+      <c r="B18" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" ht="53.25" customHeight="1">
-      <c r="B18" s="38" t="s">
+      <c r="C18" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>53</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="54" customHeight="1">
-      <c r="B19" s="38"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E19" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="76.5">
-      <c r="B20" s="38"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="23" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="35" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="102">
-      <c r="B21" s="38"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>34</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>55</v>
+        <v>78</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="63.75">
-      <c r="B22" s="38"/>
+      <c r="B22" s="39"/>
       <c r="C22" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="F22" s="35" t="s">
+        <v>106</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" ht="102">
-      <c r="B23" s="38"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="63.75">
-      <c r="B24" s="38"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="9" t="s">
         <v>29</v>
       </c>
@@ -2327,40 +2330,40 @@
         <v>31</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="140.25">
-      <c r="B25" s="38"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="24" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="204">
+      <c r="B26" s="39"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="204">
-      <c r="B26" s="38"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="34" t="s">
+      <c r="E26" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>58</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>59</v>
       </c>
       <c r="G26" s="5"/>
     </row>
